--- a/output/hasdata.com.xlsx
+++ b/output/hasdata.com.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>hasdata.com</t>
   </si>
@@ -37,40 +37,40 @@
     <t>Query: zillow api</t>
   </si>
   <si>
-    <t>Query: google scraper api</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:05:32</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:07:42</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:09:23</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:11:41</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:14:15</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:16:07</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:17:52</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:26:19</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:28:10</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:30:04</t>
-  </si>
-  <si>
-    <t>2026-03-19 02:32:13</t>
+    <t>2026-03-01 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-03 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-04 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-05 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-06 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-07 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-08 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-10 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 02:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 02:00:00</t>
   </si>
 </sst>
 </file>
@@ -473,14 +473,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="9" width="12.7109375" customWidth="1"/>
+    <col min="2" max="7" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25" customHeight="1">
+    <row r="1" spans="1:7" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,10 +490,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -507,12 +505,8 @@
         <v>6</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9">
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -534,16 +528,10 @@
       <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="8">
         <v>15</v>
@@ -551,274 +539,278 @@
       <c r="C4" s="8">
         <v>0</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="7">
+        <v>33</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
       <c r="F4" s="8">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
       </c>
-      <c r="H4" s="7">
-        <v>32</v>
-      </c>
-      <c r="I4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>36</v>
+      </c>
+      <c r="E5" s="7">
+        <v>3</v>
+      </c>
+      <c r="F5" s="8">
+        <v>29</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8">
-        <v>15</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8">
-        <v>5</v>
-      </c>
-      <c r="G5" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H5" s="7">
-        <v>24</v>
-      </c>
-      <c r="I5" s="7">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="B6" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="8">
         <v>-2</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="7">
+        <v>38</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2</v>
+      </c>
       <c r="F6" s="8">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8">
+        <v>13</v>
+      </c>
+      <c r="C7" s="8">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>35</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-3</v>
+      </c>
+      <c r="F7" s="8">
+        <v>32</v>
+      </c>
+      <c r="G7" s="8">
         <v>2</v>
       </c>
-      <c r="H6" s="7">
-        <v>59</v>
-      </c>
-      <c r="I6" s="7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="8">
-        <v>14</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7">
-        <v>59</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="B8" s="8">
         <v>14</v>
       </c>
       <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>31</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4</v>
+      </c>
+      <c r="F8" s="8">
+        <v>25</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="8">
+        <v>14</v>
+      </c>
+      <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8">
+      <c r="D9" s="7">
+        <v>31</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <v>24</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="8">
+        <v>12</v>
+      </c>
+      <c r="C10" s="8">
+        <v>-2</v>
+      </c>
+      <c r="D10" s="7">
+        <v>36</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5</v>
+      </c>
+      <c r="F10" s="8">
+        <v>27</v>
+      </c>
+      <c r="G10" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="8">
+        <v>13</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>29</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-7</v>
+      </c>
+      <c r="F11" s="8">
+        <v>22</v>
+      </c>
+      <c r="G11" s="8">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="8">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-3</v>
+      </c>
+      <c r="D12" s="7">
+        <v>28</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>20</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="8">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>21</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="8">
         <v>8</v>
       </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7">
-        <v>24</v>
-      </c>
-      <c r="I8" s="7">
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="8">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8">
-        <v>-3</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>29</v>
-      </c>
-      <c r="I9" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8">
-        <v>13</v>
-      </c>
-      <c r="C10" s="8">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8">
-        <v>6</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="C14" s="8">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>27</v>
+      </c>
+      <c r="E14" s="7">
         <v>-2</v>
       </c>
-      <c r="H10" s="7">
-        <v>24</v>
-      </c>
-      <c r="I10" s="7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="7" t="s">
+      <c r="F14" s="8">
+        <v>17</v>
+      </c>
+      <c r="G14" s="8">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="8">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>25</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2</v>
+      </c>
+      <c r="F15" s="8">
         <v>15</v>
       </c>
-      <c r="B11" s="8">
-        <v>11</v>
-      </c>
-      <c r="C11" s="8">
+      <c r="G15" s="8">
         <v>-2</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8">
-        <v>2</v>
-      </c>
-      <c r="H11" s="7">
-        <v>31</v>
-      </c>
-      <c r="I11" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="8">
-        <v>14</v>
-      </c>
-      <c r="C12" s="8">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8">
-        <v>7</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="7">
-        <v>23</v>
-      </c>
-      <c r="I12" s="7">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="8">
-        <v>14</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8">
-        <v>5</v>
-      </c>
-      <c r="G13" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H13" s="7">
-        <v>24</v>
-      </c>
-      <c r="I13" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="8">
-        <v>14</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8">
-        <v>7</v>
-      </c>
-      <c r="G14" s="8">
-        <v>2</v>
-      </c>
-      <c r="H14" s="7">
-        <v>50</v>
-      </c>
-      <c r="I14" s="7">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:I1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
